--- a/agriculture 29.xlsx
+++ b/agriculture 29.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t xml:space="preserve">2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1997-2020)</t>
@@ -147,7 +150,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -183,6 +186,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -247,7 +263,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -280,7 +296,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -301,8 +325,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB26"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="15.4"/>
@@ -1411,7 +1435,7 @@
         <v>-2.95204226081552</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
         <v>38</v>
       </c>
@@ -1429,24 +1453,43 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
+      <c r="AA26" s="10"/>
+      <c r="AB26" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A25:AB25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A26:O26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 29.xlsx
+++ b/agriculture 29.xlsx
@@ -136,7 +136,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1997-2020)</t>
@@ -150,7 +150,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -193,12 +193,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -263,7 +257,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -304,10 +298,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -326,7 +316,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="15.4"/>
@@ -1472,19 +1462,19 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
-      <c r="AB26" s="10"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/agriculture 29.xlsx
+++ b/agriculture 29.xlsx
@@ -136,7 +136,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1997-2020)</t>
@@ -316,7 +316,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="15.4"/>
